--- a/data_raw/CME_BRR_latest.xlsx
+++ b/data_raw/CME_BRR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D837"/>
+  <dimension ref="A1:D841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13826,6 +13826,70 @@
         <v>82480.33</v>
       </c>
     </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B838" t="n">
+        <v>82834.44</v>
+      </c>
+      <c r="C838" t="n">
+        <v>82976.42</v>
+      </c>
+      <c r="D838" t="n">
+        <v>82637.10000000001</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B839" t="n">
+        <v>83022.35000000001</v>
+      </c>
+      <c r="C839" t="n">
+        <v>83623.48</v>
+      </c>
+      <c r="D839" t="n">
+        <v>83003.17</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B840" t="n">
+        <v>82721.17</v>
+      </c>
+      <c r="C840" t="n">
+        <v>82528.45</v>
+      </c>
+      <c r="D840" t="n">
+        <v>84010.35000000001</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B841" t="n">
+        <v>83524.64999999999</v>
+      </c>
+      <c r="C841" t="n">
+        <v>83140.61</v>
+      </c>
+      <c r="D841" t="n">
+        <v>83733.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/CME_BRR_latest.xlsx
+++ b/data_raw/CME_BRR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D841"/>
+  <dimension ref="A1:D844"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13890,6 +13890,54 @@
         <v>83733.36</v>
       </c>
     </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B842" t="n">
+        <v>81926.14999999999</v>
+      </c>
+      <c r="C842" t="n">
+        <v>81668.06</v>
+      </c>
+      <c r="D842" t="n">
+        <v>83404.17999999999</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B843" t="n">
+        <v>81187.85000000001</v>
+      </c>
+      <c r="C843" t="n">
+        <v>82375.19</v>
+      </c>
+      <c r="D843" t="n">
+        <v>81072.55</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B844" t="n">
+        <v>82127.96000000001</v>
+      </c>
+      <c r="C844" t="n">
+        <v>81291.64</v>
+      </c>
+      <c r="D844" t="n">
+        <v>82117.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/CME_BRR_latest.xlsx
+++ b/data_raw/CME_BRR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D844"/>
+  <dimension ref="A1:D848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13938,6 +13938,70 @@
         <v>82117.66</v>
       </c>
     </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B845" t="n">
+        <v>81433.72</v>
+      </c>
+      <c r="C845" t="n">
+        <v>81455.28999999999</v>
+      </c>
+      <c r="D845" t="n">
+        <v>81559.14</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B846" t="n">
+        <v>81128.82000000001</v>
+      </c>
+      <c r="C846" t="n">
+        <v>80934.71000000001</v>
+      </c>
+      <c r="D846" t="n">
+        <v>81602.39</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B847" t="n">
+        <v>81979.94</v>
+      </c>
+      <c r="C847" t="n">
+        <v>81835.78</v>
+      </c>
+      <c r="D847" t="n">
+        <v>82779.12</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B848" t="n">
+        <v>82922.7</v>
+      </c>
+      <c r="C848" t="n">
+        <v>82443.14999999999</v>
+      </c>
+      <c r="D848" t="n">
+        <v>81543.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/CME_BRR_latest.xlsx
+++ b/data_raw/CME_BRR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D848"/>
+  <dimension ref="A1:D851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14002,6 +14002,54 @@
         <v>81543.31</v>
       </c>
     </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B849" t="n">
+        <v>84024.32000000001</v>
+      </c>
+      <c r="C849" t="n">
+        <v>84384.71000000001</v>
+      </c>
+      <c r="D849" t="n">
+        <v>82894.81</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B850" t="n">
+        <v>81662.71000000001</v>
+      </c>
+      <c r="C850" t="n">
+        <v>81313.97</v>
+      </c>
+      <c r="D850" t="n">
+        <v>82214.8</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B851" t="n">
+        <v>81556.78</v>
+      </c>
+      <c r="C851" t="n">
+        <v>81229.7</v>
+      </c>
+      <c r="D851" t="n">
+        <v>81631.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/CME_BRR_latest.xlsx
+++ b/data_raw/CME_BRR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D851"/>
+  <dimension ref="A1:D855"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14050,6 +14050,70 @@
         <v>81631.63</v>
       </c>
     </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B852" t="n">
+        <v>80255.87</v>
+      </c>
+      <c r="C852" t="n">
+        <v>80417.3</v>
+      </c>
+      <c r="D852" t="n">
+        <v>80723.27</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B853" t="n">
+        <v>80557.73</v>
+      </c>
+      <c r="C853" t="n">
+        <v>80491.95</v>
+      </c>
+      <c r="D853" t="n">
+        <v>80530.88</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B854" t="n">
+        <v>80459.36</v>
+      </c>
+      <c r="C854" t="n">
+        <v>79900.95</v>
+      </c>
+      <c r="D854" t="n">
+        <v>79975.47</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B855" t="n">
+        <v>80377.62</v>
+      </c>
+      <c r="C855" t="n">
+        <v>80602.23</v>
+      </c>
+      <c r="D855" t="n">
+        <v>79590.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/CME_BRR_latest.xlsx
+++ b/data_raw/CME_BRR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D855"/>
+  <dimension ref="A1:D858"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14114,6 +14114,54 @@
         <v>79590.38</v>
       </c>
     </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B856" t="n">
+        <v>80512.22</v>
+      </c>
+      <c r="C856" t="n">
+        <v>81185.75999999999</v>
+      </c>
+      <c r="D856" t="n">
+        <v>80829.09</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B857" t="n">
+        <v>81489.42</v>
+      </c>
+      <c r="C857" t="n">
+        <v>80753.81</v>
+      </c>
+      <c r="D857" t="n">
+        <v>79791.92999999999</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B858" t="n">
+        <v>77468.97</v>
+      </c>
+      <c r="C858" t="n">
+        <v>76467.58</v>
+      </c>
+      <c r="D858" t="n">
+        <v>78217.67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
